--- a/data/trans_bre/P1418-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1418-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,44</t>
+          <t>-0,14; 1,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,98</t>
+          <t>-1,9; 2,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>275,16%</t>
+          <t>301,69%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,51</t>
+          <t>0,58; 3,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,47</t>
+          <t>-0,25; 1,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,34</t>
+          <t>0,28; 2,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,01</t>
+          <t>-0,19; 2,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,24; 799,33</t>
+          <t>11,57; 905,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,7; —</t>
+          <t>-69,61; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>222,44%</t>
+          <t>265,36%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,44</t>
+          <t>1,55; 5,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,46</t>
+          <t>1,96; 5,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,16</t>
+          <t>1,54; 4,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,01</t>
+          <t>1,05; 4,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,53; 435,71</t>
+          <t>46,44; 453,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>111,8; 3364,29</t>
+          <t>62,95; 2960,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,03; 886,56</t>
+          <t>47,59; 978,67</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>173,17%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 8,11</t>
+          <t>1,16; 8,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,78</t>
+          <t>2,11; 6,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,02</t>
+          <t>0,34; 4,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,21</t>
+          <t>1,4; 5,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,91; 222,09</t>
+          <t>15,24; 216,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,41; 714,36</t>
+          <t>70,44; 650,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 403,77</t>
+          <t>8,87; 391,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,13; 522,12</t>
+          <t>22,94; 203,76</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>104,57%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,9</t>
+          <t>-4,24; 4,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 13,82</t>
+          <t>6,01; 13,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 9,93</t>
+          <t>3,71; 10,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,62</t>
+          <t>2,92; 7,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 52,69</t>
+          <t>-31,52; 49,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>119,58; 594,14</t>
+          <t>125,48; 623,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,3; 556,31</t>
+          <t>74,2; 580,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,27; 198,37</t>
+          <t>44,09; 210,57</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 14,82</t>
+          <t>2,7; 14,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,62; 16,15</t>
+          <t>4,75; 15,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 14,84</t>
+          <t>5,26; 14,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 5,26</t>
+          <t>1,66; 8,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,34; 127,12</t>
+          <t>14,89; 126,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,14; 213,65</t>
+          <t>35,4; 206,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,74; 351,64</t>
+          <t>50,19; 328,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-63,96; 67,2</t>
+          <t>14,51; 126,46</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,02</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 17,23</t>
+          <t>1,91; 17,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,69; 25,15</t>
+          <t>10,54; 25,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,99; 16,22</t>
+          <t>4,83; 17,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,36; 15,06</t>
+          <t>6,26; 15,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 98,4</t>
+          <t>7,67; 102,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,57; 180,78</t>
+          <t>48,91; 198,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,45; 158,78</t>
+          <t>28,49; 168,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,13; 115,26</t>
+          <t>34,93; 118,04</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,59</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>106,08%</t>
+          <t>108,22%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,01</t>
+          <t>3,4; 5,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,86</t>
+          <t>5,41; 7,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 5,85</t>
+          <t>3,69; 5,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,57</t>
+          <t>3,57; 5,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,66; 125,54</t>
+          <t>56,74; 121,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>147,61; 293,13</t>
+          <t>150,65; 288,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>129,05; 276,79</t>
+          <t>131,9; 283,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>64,14; 160,16</t>
+          <t>75,24; 146,91</t>
         </is>
       </c>
     </row>
